--- a/docs/generated/Смены.xlsx
+++ b/docs/generated/Смены.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1031,74 +1031,123 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DIM-2026-00088</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>простой — ожидание разгрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>DIM-2026-00007</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Василий Гуцу</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>Простой 1 ч — ожидание бетона</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4">
-        <f>SUM(F2:F13)</f>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4">
+        <f>SUM(F2:F14)</f>
         <v/>
       </c>
-      <c r="G14" s="4">
-        <f>SUM(G2:G13)</f>
+      <c r="G15" s="4">
+        <f>SUM(G2:G14)</f>
         <v/>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4">
-        <f>SUM(I2:I13)</f>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4">
+        <f>SUM(I2:I14)</f>
         <v/>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>

--- a/docs/generated/Смены.xlsx
+++ b/docs/generated/Смены.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1080,74 +1080,123 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DIM-2026-00097</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>простой — ожидание разгрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DIM-2026-00007</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Василий Гуцу</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Простой 1 ч — ожидание бетона</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4">
-        <f>SUM(F2:F14)</f>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4">
+        <f>SUM(F2:F15)</f>
         <v/>
       </c>
-      <c r="G15" s="4">
-        <f>SUM(G2:G14)</f>
+      <c r="G16" s="4">
+        <f>SUM(G2:G15)</f>
         <v/>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4">
-        <f>SUM(I2:I14)</f>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4">
+        <f>SUM(I2:I15)</f>
         <v/>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>

--- a/docs/generated/Смены.xlsx
+++ b/docs/generated/Смены.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1129,74 +1129,123 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DIM-2026-00106</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>простой — ожидание разгрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DIM-2026-00007</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Василий Гуцу</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>Простой 1 ч — ожидание бетона</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4">
-        <f>SUM(F2:F15)</f>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4">
+        <f>SUM(F2:F16)</f>
         <v/>
       </c>
-      <c r="G16" s="4">
-        <f>SUM(G2:G15)</f>
+      <c r="G17" s="4">
+        <f>SUM(G2:G16)</f>
         <v/>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4">
-        <f>SUM(I2:I15)</f>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4">
+        <f>SUM(I2:I16)</f>
         <v/>
       </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>

--- a/docs/generated/Смены.xlsx
+++ b/docs/generated/Смены.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1178,74 +1178,123 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DIM-2026-00112</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>простой — ожидание разгрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>DIM-2026-00007</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Василий Гуцу</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Василий Гуцу</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Простой 1 ч — ожидание бетона</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4">
-        <f>SUM(F2:F16)</f>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4">
+        <f>SUM(F2:F17)</f>
         <v/>
       </c>
-      <c r="G17" s="4">
-        <f>SUM(G2:G16)</f>
+      <c r="G18" s="4">
+        <f>SUM(G2:G17)</f>
         <v/>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4">
-        <f>SUM(I2:I16)</f>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4">
+        <f>SUM(I2:I17)</f>
         <v/>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
